--- a/DIC/Lab2/Task5/summary.xlsx
+++ b/DIC/Lab2/Task5/summary.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.088e-10</v>
+        <v>2.093e-10</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.643e-11</v>
+        <v>4.586e-11</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.196e-11</v>
+        <v>3.167e-11</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.963e-11</v>
+        <v>2.917e-11</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.912e-11</v>
+        <v>2.917e-11</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.034e-11</v>
+        <v>3.006e-11</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.182e-11</v>
+        <v>3.155e-11</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.302e-11</v>
+        <v>3.331e-11</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.487e-11</v>
+        <v>3.529e-11</v>
       </c>
     </row>
   </sheetData>
